--- a/test/Extract Pandat Results-P Ts (Lever Scheil)/Al-Cu-Li_COST/Ts-S.xlsx
+++ b/test/Extract Pandat Results-P Ts (Lever Scheil)/Al-Cu-Li_COST/Ts-S.xlsx
@@ -408,7 +408,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>778.3910852</v>
+        <v>818.3065358</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -425,7 +425,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>778.3875211</v>
+        <v>820.4791269999999</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>778.3858494</v>
+        <v>812.7919306</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -476,7 +476,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>778.3848195</v>
+        <v>812.8024538</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -493,7 +493,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>778.3901283</v>
+        <v>813.0225294000001</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -510,7 +510,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>778.3860764</v>
+        <v>817.8236263</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -527,7 +527,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>778.3855821</v>
+        <v>819.9058801</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -561,7 +561,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>778.3837007</v>
+        <v>812.7711735</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>781.9808159</v>
+        <v>843.468193</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -595,7 +595,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>778.3874831000001</v>
+        <v>812.7994505</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -612,7 +612,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>778.3906359</v>
+        <v>812.934232</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -629,7 +629,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>778.3827128</v>
+        <v>817.3447721</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -646,7 +646,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>778.3852041</v>
+        <v>819.345173</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -680,7 +680,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>778.3906947</v>
+        <v>812.7787585</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -697,7 +697,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>778.3838879</v>
+        <v>812.7888009</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -714,7 +714,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>778.3866693</v>
+        <v>812.90124</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -731,7 +731,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>778.3891827</v>
+        <v>816.7849519</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -748,7 +748,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>778.3841664</v>
+        <v>818.8625087</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -765,7 +765,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>782.4550572000001</v>
+        <v>843.4762169000001</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -799,7 +799,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>778.388547</v>
+        <v>812.7793463</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -816,7 +816,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>778.3839162</v>
+        <v>812.8009834</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -833,7 +833,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>778.3868656</v>
+        <v>812.8809218</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>778.3832998</v>
+        <v>816.3903163</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -867,7 +867,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>778.3899118</v>
+        <v>818.3044804</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -901,7 +901,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>778.3864832</v>
+        <v>812.8590787000001</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -918,7 +918,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>778.3895465000001</v>
+        <v>827.6689011</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -935,7 +935,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>778.3863282</v>
+        <v>843.474916</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -952,7 +952,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>778.3914735</v>
+        <v>843.4727576</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -969,7 +969,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>778.3849788</v>
+        <v>843.4774030999999</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>778.3908736</v>
+        <v>812.8124954</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>908.3464832</v>
+        <v>907.9464832</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -1037,7 +1037,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>778.387284</v>
+        <v>823.8287752</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>778.3855638</v>
+        <v>843.7948785999999</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -1071,7 +1071,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>778.3841158</v>
+        <v>843.4688072</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>778.3834935</v>
+        <v>843.4716392</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>778.3886675</v>
+        <v>812.7959343</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -1139,7 +1139,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>778.3876354</v>
+        <v>821.4250988</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>778.3845432000001</v>
+        <v>829.105207</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>778.3911536000001</v>
+        <v>843.4720534</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>778.3826312</v>
+        <v>843.4759302</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>778.3850126</v>
+        <v>812.7956563</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -1258,7 +1258,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>778.3842326</v>
+        <v>819.0232344999999</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>778.3860235</v>
+        <v>825.7411336</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>778.3847869</v>
+        <v>843.4783963</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -1309,7 +1309,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>778.3841972</v>
+        <v>843.4778129</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -1343,7 +1343,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>778.3848831</v>
+        <v>812.7777622999999</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -1360,7 +1360,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>778.390519</v>
+        <v>815.9884393</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>778.3825594</v>
+        <v>823.0279134</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -1411,7 +1411,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>778.3869966</v>
+        <v>843.7940005</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -1428,7 +1428,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>778.3897637</v>
+        <v>843.4755134</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>778.3830741</v>
+        <v>812.7881906</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>778.3897445</v>
+        <v>813.1758759000001</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>778.3864956</v>
+        <v>821.5008642</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -1513,7 +1513,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>778.389536</v>
+        <v>829.5853927000001</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>778.3906618</v>
+        <v>843.4681457</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -1564,7 +1564,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>778.384196</v>
+        <v>812.7827161</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72">
-        <v>778.3849586</v>
+        <v>812.9806273</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
-        <v>778.3899585</v>
+        <v>820.4254178</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -1632,7 +1632,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74">
-        <v>778.3839207</v>
+        <v>826.4695848</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>778.3879724</v>
+        <v>843.4759642</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -1683,7 +1683,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>778.3826675</v>
+        <v>812.7969494</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -1700,7 +1700,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>778.3890028</v>
+        <v>812.8977172</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>778.3848473</v>
+        <v>819.7471861</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>778.3914202</v>
+        <v>823.9042316</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>778.3825177</v>
+        <v>843.4706851</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84">
-        <v>778.3827086</v>
+        <v>812.7963375</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -1819,7 +1819,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
-        <v>778.3845035000001</v>
+        <v>812.8621357</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86">
-        <v>778.3828245</v>
+        <v>819.1820456</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -1853,7 +1853,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87">
-        <v>778.383047</v>
+        <v>822.1478341</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88">
-        <v>778.384852</v>
+        <v>839.2858962</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>778.3883329</v>
+        <v>812.7961663</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>778.3838627</v>
+        <v>812.838873</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>778.3853058</v>
+        <v>818.626247</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -1972,7 +1972,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>778.389546</v>
+        <v>821.020002</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -1989,7 +1989,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>778.385253</v>
+        <v>829.4275801</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>778.383339</v>
+        <v>812.7815653</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>778.3892488</v>
+        <v>812.8229652</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -2057,7 +2057,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>778.3834495999999</v>
+        <v>818.0665585</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -2074,7 +2074,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>778.391384</v>
+        <v>820.2217954</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -2091,7 +2091,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101">
-        <v>778.3837131</v>
+        <v>826.6247791</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -2125,7 +2125,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103">
-        <v>778.3913021</v>
+        <v>812.7975143</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -2142,7 +2142,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104">
-        <v>778.39018</v>
+        <v>816.0692656</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105">
-        <v>778.3825869</v>
+        <v>812.8095523</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
-        <v>778.3881449</v>
+        <v>817.6704531</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107">
-        <v>778.3887385</v>
+        <v>819.7461721</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -2210,7 +2210,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108">
-        <v>778.3899302999999</v>
+        <v>824.3004343</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -2244,7 +2244,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110">
-        <v>778.3855639</v>
+        <v>812.7888545</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -2261,7 +2261,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111">
-        <v>778.385548</v>
+        <v>812.8139563</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112">
-        <v>778.3900003</v>
+        <v>816.946357</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -2295,7 +2295,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113">
-        <v>778.3914855</v>
+        <v>819.2685749</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114">
-        <v>778.3833003</v>
+        <v>822.4624219</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -2329,7 +2329,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115">
-        <v>781.6606084</v>
+        <v>837.0700002999999</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -2363,7 +2363,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117">
-        <v>778.3892231999999</v>
+        <v>812.7803041</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -2380,7 +2380,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118">
-        <v>778.3895371</v>
+        <v>812.7917849</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119">
-        <v>778.3893306</v>
+        <v>815.0239822999999</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -2414,7 +2414,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120">
-        <v>778.3891884</v>
+        <v>818.787705</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121">
-        <v>778.3829081</v>
+        <v>821.3247893</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -2465,7 +2465,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123">
-        <v>778.3851249000001</v>
+        <v>812.7964805</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -2482,7 +2482,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124">
-        <v>778.3856819</v>
+        <v>812.7990695</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -2499,7 +2499,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125">
-        <v>778.3861441</v>
+        <v>813.1747752</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126">
-        <v>781.823884</v>
+        <v>843.4700779999999</v>
       </c>
       <c r="B126">
         <v>1</v>
